--- a/output/pdf_financials_xlsx/MEQ.xlsx
+++ b/output/pdf_financials_xlsx/MEQ.xlsx
@@ -20252,7 +20252,11 @@
           <t>Purchase of and additions to intangible assets</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -22636,7 +22640,11 @@
           <t>Purchase of and additions to intangible assets</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MEQ.xlsx
+++ b/output/pdf_financials_xlsx/MEQ.xlsx
@@ -2405,34 +2405,34 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.912</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.874</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.991</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.699</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.001234</v>
       </c>
     </row>
     <row r="41">
@@ -2442,34 +2442,34 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>0.912</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1.614</v>
+        <v>2.488</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.004</v>
+        <v>1.311</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.991</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>0.699</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.001234</v>
       </c>
     </row>
     <row r="42">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.782</v>
+        <v>4.87</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>8.778</v>
+        <v>8.384</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>8.393000000000001</v>
+        <v>7.519</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.479</v>
+        <v>4.172</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.69</v>
+        <v>6.493</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>7.379</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>8.901</v>
+        <v>8.372</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>31.233</v>
+        <v>30.81</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>22.65</v>
+        <v>21.951</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>22.65</v>
+        <v>22.648766</v>
       </c>
     </row>
     <row r="49">
@@ -5435,31 +5435,31 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-7.349</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-49.601</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-1.916</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-0.135</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-1.766</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-0.314</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-2.095</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-0.919</v>
       </c>
     </row>
     <row r="122">
@@ -20026,7 +20026,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -21390,7 +21394,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
